--- a/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
@@ -1563,19 +1563,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1673,7 +1673,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1747,13 +1747,13 @@
         <v>30.82224430000005</v>
       </c>
       <c r="N4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="O4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="P4" t="n">
-        <v>5.790863699999997</v>
+        <v>5.790863699999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0285</v>
@@ -1765,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>26.28542482500007</v>
+        <v>26.28542482500006</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1836,7 +1836,7 @@
         <v>3.141256800000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01200000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="R5" t="n">
         <v>30.82191780821918</v>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-8.526512829121202e-14</v>
       </c>
     </row>
     <row r="6">
@@ -1907,10 +1907,10 @@
         <v>48.08252830000018</v>
       </c>
       <c r="N6" t="n">
-        <v>332.6215999999999</v>
+        <v>332.6216</v>
       </c>
       <c r="O6" t="n">
-        <v>332.6215999999999</v>
+        <v>332.6216</v>
       </c>
       <c r="P6" t="n">
         <v>3.9914592</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4210854715202e-13</v>
+        <v>-2.842170943040401e-14</v>
       </c>
     </row>
     <row r="7">
@@ -1966,7 +1966,7 @@
         <v>390</v>
       </c>
       <c r="G7" t="n">
-        <v>250.0000000000001</v>
+        <v>250</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -1993,7 +1993,7 @@
         <v>394.7369</v>
       </c>
       <c r="P7" t="n">
-        <v>4.736842799999999</v>
+        <v>4.7368428</v>
       </c>
       <c r="Q7" t="n">
         <v>0.012</v>
@@ -2005,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>48.08255690000023</v>
+        <v>48.08255690000024</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>-1.4210854715202e-13</v>
       </c>
     </row>
   </sheetData>
@@ -9449,10 +9449,10 @@
         <v>74.73690000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>74.73690000000002</v>
+        <v>74.73690000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>74.73690000000002</v>
+        <v>74.73690000000001</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -21762,7 +21762,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8729.403761679876</v>
+        <v>8729.403761679878</v>
       </c>
     </row>
     <row r="4">
@@ -21842,7 +21842,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>950.0000000000001</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21902,7 +21902,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.899463932502157</v>
+        <v>7.899463932502158</v>
       </c>
     </row>
     <row r="11">
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.280146591136601</v>
+        <v>6.280146591136603</v>
       </c>
     </row>
     <row r="12">
@@ -21942,7 +21942,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -22062,7 +22062,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>578.8462200000001</v>
+        <v>578.84622</v>
       </c>
     </row>
     <row r="19">

--- a/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>0 / 0 / 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -778,7 +922,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -793,7 +937,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -811,7 +955,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -826,7 +970,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -843,7 +987,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -858,7 +1002,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -875,7 +1019,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -890,7 +1034,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -907,7 +1051,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -922,7 +1066,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -939,7 +1083,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -954,7 +1098,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -971,7 +1115,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -986,7 +1130,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1147,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1018,7 +1162,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1179,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1050,7 +1194,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1211,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1082,7 +1226,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1243,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1114,7 +1258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1275,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1146,7 +1290,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1307,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1178,7 +1322,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1339,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1210,7 +1354,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1371,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1242,7 +1386,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1403,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1274,7 +1418,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1435,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1306,7 +1450,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1467,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1338,7 +1482,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1499,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1370,7 +1514,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1531,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1402,7 +1546,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -11428,7 +11572,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11441,7 +11585,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11477,7 +11621,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11490,7 +11634,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11670,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11539,7 +11683,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11719,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11588,7 +11732,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11768,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11637,7 +11781,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11673,7 +11817,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11686,7 +11830,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12574,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -12440,7 +12584,7 @@
         <v/>
       </c>
       <c r="I50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -12763,7 +12907,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -12773,7 +12917,7 @@
         <v/>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -13699,7 +13843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13768,6 +13912,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13823,6 +13972,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13878,6 +14032,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13933,6 +14092,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13988,6 +14152,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14043,6 +14212,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14098,6 +14272,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14153,6 +14332,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14208,6 +14392,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14263,6 +14452,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14318,6 +14512,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14373,6 +14572,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14428,6 +14632,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14483,6 +14692,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14538,6 +14752,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14593,6 +14812,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14648,6 +14872,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14703,6 +14932,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14758,6 +14992,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14813,6 +15052,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14868,6 +15112,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14923,6 +15172,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14978,6 +15232,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15033,6 +15292,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15088,6 +15352,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15143,6 +15412,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15183,11 +15457,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2035-01</t>
+          <t>2037-01</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -15196,7 +15470,12 @@
         </is>
       </c>
       <c r="M27" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -15253,6 +15532,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15293,11 +15577,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2035-02</t>
+          <t>2037-02</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -15306,7 +15590,12 @@
         </is>
       </c>
       <c r="M29" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -15363,6 +15652,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15403,11 +15697,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2035-03</t>
+          <t>2037-03</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -15416,7 +15710,12 @@
         </is>
       </c>
       <c r="M31" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -15473,6 +15772,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15513,11 +15817,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2035-04</t>
+          <t>2037-04</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -15526,7 +15830,12 @@
         </is>
       </c>
       <c r="M33" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -15583,6 +15892,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15623,11 +15937,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2035-05</t>
+          <t>2037-05</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -15636,7 +15950,12 @@
         </is>
       </c>
       <c r="M35" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -15693,6 +16012,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15733,11 +16057,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2035-06</t>
+          <t>2037-06</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -15746,7 +16070,12 @@
         </is>
       </c>
       <c r="M37" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -15803,6 +16132,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -15843,11 +16177,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2035-07</t>
+          <t>2037-07</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -15856,7 +16190,12 @@
         </is>
       </c>
       <c r="M39" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -15913,6 +16252,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -15953,11 +16297,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2037-08</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -15966,7 +16310,12 @@
         </is>
       </c>
       <c r="M41" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -16023,6 +16372,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16063,11 +16417,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2035-09</t>
+          <t>2037-09</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -16076,7 +16430,12 @@
         </is>
       </c>
       <c r="M43" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -16133,6 +16492,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16173,11 +16537,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2035-10</t>
+          <t>2037-10</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -16186,7 +16550,12 @@
         </is>
       </c>
       <c r="M45" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -16243,6 +16612,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16283,11 +16657,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2035-11</t>
+          <t>2037-11</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -16296,7 +16670,12 @@
         </is>
       </c>
       <c r="M47" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -16353,6 +16732,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16393,11 +16777,11 @@
         <v>1.099016666666667</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2035-12</t>
+          <t>2037-12</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -16406,7 +16790,12 @@
         </is>
       </c>
       <c r="M49" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -16463,6 +16852,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16503,11 +16897,11 @@
         <v>5.98095</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2036-01</t>
+          <t>2038-01</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -16516,7 +16910,12 @@
         </is>
       </c>
       <c r="M51" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -16573,6 +16972,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -16613,11 +17017,11 @@
         <v>5.98095</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2036-02</t>
+          <t>2038-02</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -16626,7 +17030,12 @@
         </is>
       </c>
       <c r="M53" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -16683,6 +17092,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -16723,11 +17137,11 @@
         <v>5.98095</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2036-03</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -16736,7 +17150,12 @@
         </is>
       </c>
       <c r="M55" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -16793,6 +17212,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -16833,11 +17257,11 @@
         <v>5.98095</v>
       </c>
       <c r="J57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2036-04</t>
+          <t>2038-04</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -16846,7 +17270,12 @@
         </is>
       </c>
       <c r="M57" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -16903,6 +17332,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16943,11 +17377,11 @@
         <v>5.98095</v>
       </c>
       <c r="J59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2036-05</t>
+          <t>2038-05</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -16956,7 +17390,12 @@
         </is>
       </c>
       <c r="M59" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -17013,6 +17452,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17053,11 +17497,11 @@
         <v>5.98095</v>
       </c>
       <c r="J61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2036-06</t>
+          <t>2038-06</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -17066,7 +17510,12 @@
         </is>
       </c>
       <c r="M61" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -17123,6 +17572,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17163,11 +17617,11 @@
         <v>5.98095</v>
       </c>
       <c r="J63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2036-07</t>
+          <t>2038-07</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -17176,7 +17630,12 @@
         </is>
       </c>
       <c r="M63" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -17233,6 +17692,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17273,11 +17737,11 @@
         <v>5.98095</v>
       </c>
       <c r="J65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2038-08</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -17286,7 +17750,12 @@
         </is>
       </c>
       <c r="M65" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -17343,6 +17812,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17383,11 +17857,11 @@
         <v>5.98095</v>
       </c>
       <c r="J67" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2036-09</t>
+          <t>2038-09</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -17396,7 +17870,12 @@
         </is>
       </c>
       <c r="M67" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -17453,6 +17932,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17493,11 +17977,11 @@
         <v>5.98095</v>
       </c>
       <c r="J69" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2036-10</t>
+          <t>2038-10</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -17506,7 +17990,12 @@
         </is>
       </c>
       <c r="M69" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -17563,6 +18052,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17603,11 +18097,11 @@
         <v>5.98095</v>
       </c>
       <c r="J71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2036-11</t>
+          <t>2038-11</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -17616,7 +18110,12 @@
         </is>
       </c>
       <c r="M71" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -17673,6 +18172,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -17713,11 +18217,11 @@
         <v>5.98095</v>
       </c>
       <c r="J73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2036-12</t>
+          <t>2038-12</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -17726,7 +18230,12 @@
         </is>
       </c>
       <c r="M73" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -17783,6 +18292,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -17838,6 +18352,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -17878,20 +18397,25 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J76" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t>2039-01</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t>2037-01</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>2037-01</t>
-        </is>
-      </c>
       <c r="M76" t="b">
         <v>1</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -17948,6 +18472,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18003,6 +18532,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18043,11 +18577,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J79" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2037-02</t>
+          <t>2039-02</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -18057,6 +18591,11 @@
       </c>
       <c r="M79" t="b">
         <v>1</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -18113,6 +18652,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18168,6 +18712,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18208,11 +18757,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J82" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2037-03</t>
+          <t>2039-03</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -18222,6 +18771,11 @@
       </c>
       <c r="M82" t="b">
         <v>1</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -18278,6 +18832,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18333,6 +18892,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18373,11 +18937,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J85" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2037-04</t>
+          <t>2039-04</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -18387,6 +18951,11 @@
       </c>
       <c r="M85" t="b">
         <v>1</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -18443,6 +19012,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18498,6 +19072,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -18538,11 +19117,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J88" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2037-05</t>
+          <t>2039-05</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -18552,6 +19131,11 @@
       </c>
       <c r="M88" t="b">
         <v>1</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -18608,6 +19192,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18663,6 +19252,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -18703,11 +19297,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J91" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2037-06</t>
+          <t>2039-06</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -18717,6 +19311,11 @@
       </c>
       <c r="M91" t="b">
         <v>1</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -18773,6 +19372,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -18828,6 +19432,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -18868,11 +19477,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J94" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2037-07</t>
+          <t>2039-07</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -18882,6 +19491,11 @@
       </c>
       <c r="M94" t="b">
         <v>1</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -18938,6 +19552,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -18993,6 +19612,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19033,11 +19657,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J97" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2039-08</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -19047,6 +19671,11 @@
       </c>
       <c r="M97" t="b">
         <v>1</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -19103,6 +19732,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -19158,6 +19792,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19198,11 +19837,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J100" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2037-09</t>
+          <t>2039-09</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -19212,6 +19851,11 @@
       </c>
       <c r="M100" t="b">
         <v>1</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -19268,6 +19912,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19323,6 +19972,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19363,11 +20017,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J103" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2037-10</t>
+          <t>2039-10</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -19377,6 +20031,11 @@
       </c>
       <c r="M103" t="b">
         <v>1</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -19433,6 +20092,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19488,6 +20152,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19528,11 +20197,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J106" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2037-11</t>
+          <t>2039-11</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -19542,6 +20211,11 @@
       </c>
       <c r="M106" t="b">
         <v>1</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -19598,6 +20272,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -19653,6 +20332,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -19693,11 +20377,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J109" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2037-12</t>
+          <t>2039-12</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -19707,6 +20391,11 @@
       </c>
       <c r="M109" t="b">
         <v>1</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -19763,6 +20452,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -19818,6 +20512,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -19858,11 +20557,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J112" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2038-01</t>
+          <t>2040-01</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -19872,6 +20571,11 @@
       </c>
       <c r="M112" t="b">
         <v>1</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -19928,6 +20632,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -19983,6 +20692,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20023,11 +20737,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J115" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2038-02</t>
+          <t>2040-02</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -20037,6 +20751,11 @@
       </c>
       <c r="M115" t="b">
         <v>1</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -20093,6 +20812,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20148,6 +20872,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20188,11 +20917,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J118" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2038-03</t>
+          <t>2040-03</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -20202,6 +20931,11 @@
       </c>
       <c r="M118" t="b">
         <v>1</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -20258,6 +20992,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20313,6 +21052,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20353,11 +21097,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J121" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2038-04</t>
+          <t>2040-04</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -20367,6 +21111,11 @@
       </c>
       <c r="M121" t="b">
         <v>1</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -20423,6 +21172,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20478,6 +21232,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20518,11 +21277,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J124" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2038-05</t>
+          <t>2040-05</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -20532,6 +21291,11 @@
       </c>
       <c r="M124" t="b">
         <v>1</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -20588,6 +21352,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -20643,6 +21412,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -20683,11 +21457,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J127" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2038-06</t>
+          <t>2040-06</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -20697,6 +21471,11 @@
       </c>
       <c r="M127" t="b">
         <v>1</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -20753,6 +21532,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -20808,6 +21592,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -20848,11 +21637,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J130" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2038-07</t>
+          <t>2040-07</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -20862,6 +21651,11 @@
       </c>
       <c r="M130" t="b">
         <v>1</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -20918,6 +21712,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -20973,6 +21772,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21013,11 +21817,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J133" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2040-08</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -21027,6 +21831,11 @@
       </c>
       <c r="M133" t="b">
         <v>1</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -21083,6 +21892,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21138,6 +21952,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21178,11 +21997,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J136" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2038-09</t>
+          <t>2040-09</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -21192,6 +22011,11 @@
       </c>
       <c r="M136" t="b">
         <v>1</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -21248,6 +22072,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21303,6 +22132,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21343,11 +22177,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J139" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2038-10</t>
+          <t>2040-10</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -21357,6 +22191,11 @@
       </c>
       <c r="M139" t="b">
         <v>1</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -21413,6 +22252,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -21468,6 +22312,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -21508,11 +22357,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J142" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2038-11</t>
+          <t>2040-11</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -21522,6 +22371,11 @@
       </c>
       <c r="M142" t="b">
         <v>1</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -21578,6 +22432,11 @@
       <c r="M143" t="b">
         <v>1</v>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -21633,6 +22492,11 @@
       <c r="M144" t="b">
         <v>1</v>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -21673,11 +22537,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J145" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2038-12</t>
+          <t>2040-12</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -21687,6 +22551,11 @@
       </c>
       <c r="M145" t="b">
         <v>1</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -22282,7 +23151,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,6 +1547,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -11561,18 +11594,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11585,7 +11618,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11610,18 +11643,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11634,7 +11667,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11659,18 +11692,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11683,7 +11716,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11708,18 +11741,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11732,7 +11765,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11757,18 +11790,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11781,7 +11814,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11806,18 +11839,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11830,7 +11863,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11888,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -11879,7 +11912,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12123,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -12114,7 +12147,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12325,11 +12358,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>30.82224430000005</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G45" t="n">
         <v>70</v>
@@ -12349,7 +12382,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12691,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -12682,7 +12715,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12991,7 +13024,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -13015,7 +13048,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13455,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -13446,7 +13479,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1579,6 +1579,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
@@ -7542,7 +7542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7651,6 +7651,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7726,6 +7731,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7801,6 +7809,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7876,6 +7887,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7951,6 +7965,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8026,6 +8043,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8101,6 +8121,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8176,6 +8199,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8251,6 +8277,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8326,6 +8355,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8401,6 +8433,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8476,6 +8511,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8551,6 +8589,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8626,6 +8667,9 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8701,6 +8745,9 @@
       <c r="U15" t="n">
         <v>3.9567</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8776,6 +8823,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8851,6 +8901,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8926,6 +8979,9 @@
       <c r="U18" t="n">
         <v>85.5</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9001,6 +9057,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9076,6 +9135,9 @@
       <c r="U20" t="n">
         <v>21.5316</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9151,6 +9213,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9226,6 +9291,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9301,6 +9369,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9376,6 +9447,9 @@
       <c r="U24" t="n">
         <v>1.8933</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9451,6 +9525,9 @@
       <c r="U25" t="n">
         <v>39</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9526,6 +9603,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9601,6 +9681,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9676,6 +9759,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9751,6 +9837,9 @@
       <c r="U29" t="n">
         <v>11.21055</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9826,6 +9915,9 @@
       <c r="U30" t="n">
         <v>39</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9901,6 +9993,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9974,6 +10069,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9988,7 +10086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10052,6 +10150,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10094,6 +10197,9 @@
       <c r="L2" t="n">
         <v>360</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10136,6 +10242,9 @@
       <c r="L3" t="n">
         <v>360</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10178,6 +10287,9 @@
       <c r="L4" t="n">
         <v>540</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10220,6 +10332,9 @@
       <c r="L5" t="n">
         <v>540</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10262,6 +10377,9 @@
       <c r="L6" t="n">
         <v>540</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10303,6 +10421,9 @@
       </c>
       <c r="L7" t="n">
         <v>540</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -22701,7 +22822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23139,11 +23260,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -23159,11 +23280,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>48.08258550000031</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -23179,11 +23300,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>48.08258550000031</v>
       </c>
     </row>
     <row r="25">
@@ -23199,7 +23320,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -23219,7 +23340,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -23239,11 +23360,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -23259,11 +23380,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>75</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -23279,10 +23400,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>75</v>
       </c>
     </row>

--- a/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
+++ b/results/alternatives/P2z_earth_new_zbo_BASE/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -874,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,7 +1400,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1418,24 +1420,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1445,29 +1447,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1477,29 +1479,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1509,176 +1511,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2415,6 +2560,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2487,6 +2642,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2558,6 +2719,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2629,6 +2796,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2700,6 +2873,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2771,6 +2950,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2842,6 +3027,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2913,6 +3104,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2984,6 +3181,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3055,6 +3258,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3126,6 +3335,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3197,6 +3412,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3268,6 +3489,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3339,6 +3566,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3410,6 +3643,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3481,6 +3720,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3552,6 +3797,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3623,6 +3874,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3694,6 +3951,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3765,6 +4028,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3836,6 +4105,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3907,6 +4182,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3978,6 +4259,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4049,6 +4336,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4120,6 +4413,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4191,6 +4490,12 @@
         <v>1.415606307500004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.59530225000007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4262,6 +4567,12 @@
         <v>1.435829962500004</v>
       </c>
       <c r="U27" t="n">
+        <v>39.93236316666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4333,6 +4644,12 @@
         <v>1.456053617500004</v>
       </c>
       <c r="U28" t="n">
+        <v>40.2694240833334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4404,6 +4721,12 @@
         <v>1.476277272500004</v>
       </c>
       <c r="U29" t="n">
+        <v>40.60648500000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4475,6 +4798,12 @@
         <v>1.496500927500004</v>
       </c>
       <c r="U30" t="n">
+        <v>40.94354591666674</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4546,6 +4875,12 @@
         <v>1.516724582500004</v>
       </c>
       <c r="U31" t="n">
+        <v>41.2806068333334</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4617,6 +4952,12 @@
         <v>1.553711264000004</v>
       </c>
       <c r="U32" t="n">
+        <v>42.17643530000007</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4688,6 +5029,12 @@
         <v>1.607460972000004</v>
       </c>
       <c r="U33" t="n">
+        <v>43.07226376666673</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4759,6 +5106,12 @@
         <v>1.661210680000003</v>
       </c>
       <c r="U34" t="n">
+        <v>43.96809223333339</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4830,6 +5183,12 @@
         <v>1.714960388000003</v>
       </c>
       <c r="U35" t="n">
+        <v>44.86392070000006</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4901,6 +5260,12 @@
         <v>1.768710096000003</v>
       </c>
       <c r="U36" t="n">
+        <v>45.75974916666672</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4972,6 +5337,12 @@
         <v>1.822459804000003</v>
       </c>
       <c r="U37" t="n">
+        <v>46.65557763333339</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5043,6 +5414,12 @@
         <v>1.870910016000003</v>
       </c>
       <c r="U38" t="n">
+        <v>52.37475623333339</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5114,6 +5491,12 @@
         <v>1.914060732000004</v>
       </c>
       <c r="U39" t="n">
+        <v>53.09393483333339</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5185,6 +5568,12 @@
         <v>1.957211448000004</v>
       </c>
       <c r="U40" t="n">
+        <v>53.8131134333334</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5256,6 +5645,12 @@
         <v>2.000362164000004</v>
       </c>
       <c r="U41" t="n">
+        <v>54.53229203333341</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5327,6 +5722,12 @@
         <v>2.043512880000005</v>
       </c>
       <c r="U42" t="n">
+        <v>55.25147063333341</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5398,6 +5799,12 @@
         <v>2.086663596000005</v>
       </c>
       <c r="U43" t="n">
+        <v>55.97064923333342</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5469,6 +5876,12 @@
         <v>2.129814312000005</v>
       </c>
       <c r="U44" t="n">
+        <v>56.68982783333342</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5540,6 +5953,12 @@
         <v>2.172965028000006</v>
       </c>
       <c r="U45" t="n">
+        <v>57.40900643333343</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5611,6 +6030,12 @@
         <v>2.216115744000006</v>
       </c>
       <c r="U46" t="n">
+        <v>58.12818503333344</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5682,6 +6107,12 @@
         <v>2.259266460000007</v>
       </c>
       <c r="U47" t="n">
+        <v>58.84736363333344</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5753,6 +6184,12 @@
         <v>2.302417176000007</v>
       </c>
       <c r="U48" t="n">
+        <v>59.56654223333345</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5824,6 +6261,12 @@
         <v>2.345567892000008</v>
       </c>
       <c r="U49" t="n">
+        <v>60.28572083333346</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5895,6 +6338,12 @@
         <v>2.388718602000008</v>
       </c>
       <c r="U50" t="n">
+        <v>66.83823256666679</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5966,6 +6415,12 @@
         <v>2.431869306000008</v>
       </c>
       <c r="U51" t="n">
+        <v>67.55741096666679</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6037,6 +6492,12 @@
         <v>2.475020010000008</v>
       </c>
       <c r="U52" t="n">
+        <v>68.2765893666668</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6108,6 +6569,12 @@
         <v>2.518170714000008</v>
       </c>
       <c r="U53" t="n">
+        <v>68.9957677666668</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6179,6 +6646,12 @@
         <v>2.561321418000009</v>
       </c>
       <c r="U54" t="n">
+        <v>69.71494616666681</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6250,6 +6723,12 @@
         <v>2.604472122000009</v>
       </c>
       <c r="U55" t="n">
+        <v>70.43412456666681</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6321,6 +6800,12 @@
         <v>2.647622826000009</v>
       </c>
       <c r="U56" t="n">
+        <v>71.15330296666681</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6392,6 +6877,12 @@
         <v>2.69077353000001</v>
       </c>
       <c r="U57" t="n">
+        <v>71.87248136666682</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6463,6 +6954,12 @@
         <v>2.73392423400001</v>
       </c>
       <c r="U58" t="n">
+        <v>72.59165976666682</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6534,6 +7031,12 @@
         <v>2.77707493800001</v>
       </c>
       <c r="U59" t="n">
+        <v>73.31083816666683</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6605,6 +7108,12 @@
         <v>2.82022564200001</v>
       </c>
       <c r="U60" t="n">
+        <v>74.03001656666683</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6676,6 +7185,12 @@
         <v>2.86337634600001</v>
       </c>
       <c r="U61" t="n">
+        <v>74.74919496666683</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6747,6 +7262,12 @@
         <v>2.884951841000011</v>
       </c>
       <c r="U62" t="n">
+        <v>80.58253306666685</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6818,6 +7339,12 @@
         <v>2.884952127000011</v>
       </c>
       <c r="U63" t="n">
+        <v>80.58253783333353</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6889,6 +7416,12 @@
         <v>2.884952413000012</v>
       </c>
       <c r="U64" t="n">
+        <v>80.58254260000021</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6960,6 +7493,12 @@
         <v>2.884952699000013</v>
       </c>
       <c r="U65" t="n">
+        <v>80.58254736666689</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7031,6 +7570,12 @@
         <v>2.884952985000014</v>
       </c>
       <c r="U66" t="n">
+        <v>80.58255213333356</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7102,6 +7647,12 @@
         <v>2.884953271000014</v>
       </c>
       <c r="U67" t="n">
+        <v>80.58255690000024</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7173,6 +7724,12 @@
         <v>2.884953557000015</v>
       </c>
       <c r="U68" t="n">
+        <v>80.58256166666692</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7244,6 +7801,12 @@
         <v>2.884953843000015</v>
       </c>
       <c r="U69" t="n">
+        <v>80.5825664333336</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7315,6 +7878,12 @@
         <v>2.884954129000016</v>
       </c>
       <c r="U70" t="n">
+        <v>80.58257120000027</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7386,6 +7955,12 @@
         <v>2.884954415000017</v>
       </c>
       <c r="U71" t="n">
+        <v>80.58257596666695</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7457,6 +8032,12 @@
         <v>2.884954701000017</v>
       </c>
       <c r="U72" t="n">
+        <v>80.58258073333363</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7528,6 +8109,12 @@
         <v>2.884954987000018</v>
       </c>
       <c r="U73" t="n">
+        <v>80.58258550000031</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10177,7 +10764,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10186,13 +10773,13 @@
         <v>360</v>
       </c>
       <c r="I2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="L2" t="n">
         <v>360</v>
@@ -10458,7 +11045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12149,7 +12736,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -12157,14 +12744,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G36" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -12181,7 +12768,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12785,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -12206,14 +12793,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>109.876</v>
       </c>
       <c r="G37" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -12247,7 +12834,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -12255,18 +12842,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -12276,7 +12864,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12291,7 +12883,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12299,7 +12891,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -12335,27 +12927,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -12365,11 +12956,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12384,7 +12971,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12392,14 +12979,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G41" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -12416,7 +13003,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12433,7 +13020,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12441,14 +13028,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G42" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -12465,7 +13052,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12482,7 +13069,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -12490,170 +13077,170 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G43" t="n">
+        <v>190</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G44" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <f>=</f>
         <v/>
       </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D46" t="n">
         <v>2036</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44">
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <f>=</f>
         <v/>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>25.44727350000007</v>
-      </c>
-      <c r="G45" t="n">
-        <v>70</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>190</v>
-      </c>
-      <c r="G46" t="n">
-        <v>190</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12668,7 +13255,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -12676,14 +13263,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>190</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G47" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -12700,7 +13287,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12717,7 +13304,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -12725,14 +13312,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>13.189</v>
+        <v>41.2806068333334</v>
       </c>
       <c r="G48" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -12749,7 +13336,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12766,7 +13353,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -12774,14 +13361,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>13.1882</v>
+        <v>190</v>
       </c>
       <c r="G49" t="n">
-        <v>13.189</v>
+        <v>190</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -12798,7 +13385,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -12815,7 +13402,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -12823,219 +13410,219 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>190</v>
+      </c>
+      <c r="G50" t="n">
+        <v>190</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="G51" t="n">
+        <v>130</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>13.1882</v>
+      </c>
+      <c r="G52" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53">
         <f>=</f>
         <v/>
       </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D54" t="n">
         <v>2037</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51">
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54">
         <f>=</f>
         <v/>
       </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>39.45238750000013</v>
-      </c>
-      <c r="G52" t="n">
-        <v>120</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>190</v>
-      </c>
-      <c r="G53" t="n">
-        <v>190</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>190</v>
-      </c>
-      <c r="G54" t="n">
-        <v>190</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13050,7 +13637,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -13058,14 +13645,14 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>71.77200000000001</v>
+        <v>39.45238750000013</v>
       </c>
       <c r="G55" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -13082,7 +13669,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13686,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -13107,14 +13694,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>71.7714</v>
+        <v>60.28572083333346</v>
       </c>
       <c r="G56" t="n">
-        <v>71.77200000000001</v>
+        <v>120</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -13131,7 +13718,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2038-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13735,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -13156,268 +13743,268 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>190</v>
+      </c>
+      <c r="G57" t="n">
+        <v>190</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>190</v>
+      </c>
+      <c r="G58" t="n">
+        <v>190</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>71.77200000000001</v>
+      </c>
+      <c r="G59" t="n">
+        <v>130</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>71.7714</v>
+      </c>
+      <c r="G60" t="n">
+        <v>71.77200000000001</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57">
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61">
         <f>=</f>
         <v/>
       </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D62" t="n">
         <v>2038</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58">
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62">
         <f>=</f>
         <v/>
       </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>48.08252830000018</v>
-      </c>
-      <c r="G59" t="n">
-        <v>120</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2039-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>190</v>
-      </c>
-      <c r="G60" t="n">
-        <v>190</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>190</v>
-      </c>
-      <c r="G61" t="n">
-        <v>190</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>12.622</v>
-      </c>
-      <c r="G62" t="n">
-        <v>110</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13432,7 +14019,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -13440,14 +14027,14 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>12.6216</v>
+        <v>48.08252830000018</v>
       </c>
       <c r="G63" t="n">
-        <v>12.622</v>
+        <v>120</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -13464,7 +14051,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13481,7 +14068,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -13489,14 +14076,14 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>130</v>
+        <v>74.74919496666683</v>
       </c>
       <c r="G64" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -13513,7 +14100,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2039-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13530,7 +14117,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -13538,14 +14125,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="G65" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -13562,7 +14149,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13579,7 +14166,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -13587,317 +14174,317 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>190</v>
+      </c>
+      <c r="G66" t="n">
+        <v>190</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>12.622</v>
+      </c>
+      <c r="G67" t="n">
+        <v>110</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>12.6216</v>
+      </c>
+      <c r="G68" t="n">
+        <v>12.622</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>130</v>
+      </c>
+      <c r="G69" t="n">
+        <v>130</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>130</v>
+      </c>
+      <c r="G70" t="n">
+        <v>130</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66">
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71">
         <f>=</f>
         <v/>
       </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D72" t="n">
         <v>2039</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67">
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72">
         <f>=</f>
         <v/>
       </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>48.08258550000031</v>
-      </c>
-      <c r="G68" t="n">
-        <v>120</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2040-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>190</v>
-      </c>
-      <c r="G69" t="n">
-        <v>190</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>190</v>
-      </c>
-      <c r="G70" t="n">
-        <v>190</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>74.73699999999999</v>
-      </c>
-      <c r="G71" t="n">
-        <v>110</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>74.73690000000001</v>
-      </c>
-      <c r="G72" t="n">
-        <v>74.73699999999999</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13912,7 +14499,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -13920,14 +14507,14 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>130</v>
+        <v>48.08258550000031</v>
       </c>
       <c r="G73" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -13944,7 +14531,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13961,7 +14548,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -13969,14 +14556,14 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>130</v>
+        <v>80.58258550000031</v>
       </c>
       <c r="G74" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -13993,7 +14580,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2040-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14597,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -14018,72 +14605,366 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>190</v>
+      </c>
+      <c r="G75" t="n">
+        <v>190</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>190</v>
+      </c>
+      <c r="G76" t="n">
+        <v>190</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>74.73699999999999</v>
+      </c>
+      <c r="G77" t="n">
+        <v>110</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>74.73690000000001</v>
+      </c>
+      <c r="G78" t="n">
+        <v>74.73699999999999</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>130</v>
+      </c>
+      <c r="G79" t="n">
+        <v>130</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>130</v>
+      </c>
+      <c r="G80" t="n">
+        <v>130</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75">
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81">
         <f>=</f>
         <v/>
       </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>P2z_earth_new_zbo</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D82" t="n">
         <v>2040</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76">
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82">
         <f>=</f>
         <v/>
       </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22822,7 +23703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22864,7 +23745,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10980.254866178</v>
+        <v>10980.624731948</v>
       </c>
     </row>
     <row r="3">
@@ -22884,7 +23765,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8729.403761679878</v>
+        <v>8729.773627449877</v>
       </c>
     </row>
     <row r="4">
@@ -23024,7 +23905,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.899463932502158</v>
+        <v>7.899730022984174</v>
       </c>
     </row>
     <row r="11">
@@ -23044,7 +23925,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.280146591136603</v>
+        <v>6.280412681618616</v>
       </c>
     </row>
     <row r="12">
@@ -23204,7 +24085,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>135.6552561780004</v>
+        <v>136.0251219480004</v>
       </c>
     </row>
     <row r="20">
@@ -23320,11 +24201,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -23340,11 +24221,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -23360,7 +24241,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -23380,11 +24261,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -23400,11 +24281,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -23420,11 +24301,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P2z_earth_new_zbo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>75</v>
+      <c r="D32" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
